--- a/library/cost_library_template.xlsx
+++ b/library/cost_library_template.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2747,12 +2747,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jumper_rigid</t>
+          <t>slot_tiein</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rigid spool/jumper</t>
+          <t>Template slot tie-in (integral)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2766,24 +2766,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>800000</v>
+        <v>250000</v>
       </c>
       <c r="F26" t="n">
-        <v>700000</v>
+        <v>150000</v>
       </c>
       <c r="G26" t="n">
         <v>0.08</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>rig</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>10000</v>
@@ -2798,11 +2798,11 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fabricated after metrology; lead time from metrology</t>
+          <t>XT landed directly in the template flowbase — no fabricated spool</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -2812,16 +2812,24 @@
       <c r="S26" t="n">
         <v>0</v>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>#6F6F6F</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2 3</t>
+        </is>
+      </c>
       <c r="V26" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0.9</v>
@@ -2836,29 +2844,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>riser_flex</t>
+          <t>jumper_rigid</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Flexible dynamic riser</t>
+          <t>Rigid spool/jumper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>riser</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>420</v>
+        <v>800000</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="G27" t="n">
         <v>0.08</v>
@@ -2869,10 +2877,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
         <v>10000</v>
@@ -2881,15 +2889,19 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>120</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fabricated after metrology; lead time from metrology</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
@@ -2897,20 +2909,16 @@
       <c r="S27" t="n">
         <v>0</v>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>#7D4EBF</t>
-        </is>
-      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W27" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y27" t="n">
         <v>0.9</v>
@@ -2925,26 +2933,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>umb_power</t>
+          <t>riser_flex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Electro-hydraulic umbilical with power cores</t>
+          <t>Flexible dynamic riser</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>umbilical</t>
+          <t>riser</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1500</v>
+        <v>420</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2954,14 +2962,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K28" t="n">
         <v>10000</v>
@@ -2970,19 +2978,15 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>32</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Control, chemical and LV/MV power in one umbilical</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
@@ -2992,22 +2996,18 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>#B3801A</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>8 6</t>
-        </is>
-      </c>
+          <t>#7D4EBF</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y28" t="n">
         <v>0.9</v>
@@ -3022,17 +3022,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chem_line</t>
+          <t>umb_power</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chemical injection line (MEG/methanol)</t>
+          <t>Electro-hydraulic umbilical with power cores</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>umbilical</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>260</v>
+        <v>1500</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
         <v>10000</v>
@@ -3073,11 +3073,11 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stand-alone bulk chemical line; often piggybacked on the flowline</t>
+          <t>Control, chemical and LV/MV power in one umbilical</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>#9DBA00</t>
+          <t>#B3801A</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>4 4</t>
+          <t>8 6</t>
         </is>
       </c>
       <c r="V29" t="n">
@@ -3119,12 +3119,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gaslift_line</t>
+          <t>chem_line</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gas lift line</t>
+          <t>Chemical injection line (MEG/methanol)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3134,28 +3134,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>per_m</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="F30" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0.08</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>ulv</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
         <v>10000</v>
@@ -3164,15 +3164,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>70</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stand-alone bulk chemical line; often piggybacked on the flowline</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>0</v>
@@ -3182,22 +3186,22 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>#5B8FB9</t>
+          <t>#9DBA00</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>10 4</t>
+          <t>4 4</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0.9</v>
@@ -3212,12 +3216,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>winj_line</t>
+          <t>gaslift_line</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Water injection flowline</t>
+          <t>Gas lift line</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3231,10 +3235,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
         <v>0.08</v>
@@ -3257,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -3275,10 +3279,14 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>#2E86AB</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
+          <t>#5B8FB9</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>10 4</t>
+        </is>
+      </c>
       <c r="V31" t="n">
         <v>0.5</v>
       </c>
@@ -3301,12 +3309,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>service_line</t>
+          <t>winj_line</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hydraulic/service line</t>
+          <t>Water injection flowline</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3316,25 +3324,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G32" t="n">
         <v>0.08</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J32" t="n">
         <v>12</v>
@@ -3346,13 +3354,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -3364,22 +3372,18 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>#8C6D1F</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>3 5</t>
-        </is>
-      </c>
+          <t>#2E86AB</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y32" t="n">
         <v>0.9</v>
@@ -3394,12 +3398,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fibre_cable</t>
+          <t>service_line</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fibre-optic cable</t>
+          <t>Hydraulic/service line</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3413,7 +3417,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3445,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -3457,12 +3461,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>#6F6F6F</t>
+          <t>#8C6D1F</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1 5</t>
+          <t>3 5</t>
         </is>
       </c>
       <c r="V33" t="n">
@@ -3487,17 +3491,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pwr_cable</t>
+          <t>fibre_cable</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Subsea power cable (HV)</t>
+          <t>Fibre-optic cable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>power_cable</t>
+          <t>utility_line</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3506,7 +3510,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1600</v>
+        <v>120</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3520,10 +3524,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
         <v>10000</v>
@@ -3538,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -3550,12 +3554,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>#C4561B</t>
+          <t>#6F6F6F</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2 6</t>
+          <t>1 5</t>
         </is>
       </c>
       <c r="V34" t="n">
@@ -3574,6 +3578,99 @@
         <v>1</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>pwr_cable</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Subsea power cable (HV)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>power_cable</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>24</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>40</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>#C4561B</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2 6</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>1.3</v>
       </c>
     </row>

--- a/library/cost_library_template.xlsx
+++ b/library/cost_library_template.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1744,17 +1744,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>riser_base</t>
+          <t>plet_valved</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Riser base</t>
+          <t>PLET with isolation valve</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>riser_base</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3000000</v>
+        <v>3200000</v>
       </c>
       <c r="F15" t="n">
-        <v>2000000</v>
+        <v>1400000</v>
       </c>
       <c r="G15" t="n">
         <v>0.08</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>14</v>
@@ -1795,19 +1795,23 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>120</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Remote-operated valve lets the line be isolated at the end structure</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>riser_base</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="R15" t="n">
         <v>14</v>
       </c>
       <c r="S15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1833,17 +1837,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>host_tiein</t>
+          <t>plet_pig</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Host tie-in modification (topsides)</t>
+          <t>PLET with subsea pig launcher/receiver</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1852,24 +1856,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25000000</v>
+        <v>4500000</v>
       </c>
       <c r="F16" t="n">
-        <v>15000000</v>
+        <v>2000000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
         <v>10000</v>
@@ -1884,23 +1888,23 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Receiving facilities, pig receiver, control/HPU, chemical injection</t>
+          <t>For single-line (non-looped) systems that still need pigging</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="S16" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -1920,23 +1924,23 @@
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>host_semi</t>
+          <t>wye_pig</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Host tie-in — semi-submersible</t>
+          <t>Piggable wye (Y-piece)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1945,24 +1949,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30000000</v>
+        <v>3000000</v>
       </c>
       <c r="F17" t="n">
-        <v>18000000</v>
+        <v>1200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
         <v>10000</v>
@@ -1977,23 +1981,23 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Floater tie-in: riser porch/pull-in, receiving facilities, utilities</t>
+          <t>Joins two lines into one while keeping it piggable</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>semisub</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2013,23 +2017,23 @@
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>host_fpso</t>
+          <t>hot_tap</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Host tie-in — FPSO</t>
+          <t>Hot-tap tie-in to an operating pipeline</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2038,24 +2042,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>35000000</v>
+        <v>6000000</v>
       </c>
       <c r="F18" t="n">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
         <v>10000</v>
@@ -2070,23 +2074,23 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>400</v>
+        <v>35</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Turret/swivel slot, riser pull-in, topsides tie-in</t>
+          <t>Tee welded/clamped onto a live line; includes hot-tap machine and diving/ROV spread time</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>fpso</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -2106,49 +2110,49 @@
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fl_rigid_cs</t>
+          <t>hipps_mod</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rigid CS flowline (coated)</t>
+          <t>HIPPS module (subsea)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>ssiv</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>12000000</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>3000000</v>
       </c>
       <c r="G19" t="n">
         <v>0.08</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K19" t="n">
         <v>10000</v>
@@ -2157,36 +2161,40 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>90</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tick HIPPS on the node so lines downstream may be de-rated</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ssiv</t>
+        </is>
+      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>#00243D</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0.9</v>
@@ -2201,43 +2209,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fl_rigid_cra</t>
+          <t>pump_1ph</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rigid CRA-lined flowline</t>
+          <t>Single-phase booster pump station (liquid)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>boosting</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>260</v>
+        <v>45000000</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>15000000</v>
       </c>
       <c r="G20" t="n">
         <v>0.08</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n">
         <v>10000</v>
@@ -2246,36 +2254,40 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>95</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Centrifugal pump for oil or water with low gas fraction (typically GVF &lt; 15 %)</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>#004B6B</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0.9</v>
@@ -2284,49 +2296,49 @@
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fl_pip</t>
+          <t>pump_mp1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pipe-in-pipe insulated flowline</t>
+          <t>Multiphase pump module (single, retrievable)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>boosting</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>240</v>
+        <v>50000000</v>
       </c>
       <c r="F21" t="n">
-        <v>110</v>
+        <v>15000000</v>
       </c>
       <c r="G21" t="n">
         <v>0.08</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
         <v>10000</v>
@@ -2335,36 +2347,40 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>160</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>180</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Helico-axial or twin-screw; handles high gas fractions without separation</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>#0F7A8A</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0.9</v>
@@ -2373,49 +2389,49 @@
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fl_deh</t>
+          <t>winj_pump</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEH heated rigid flowline</t>
+          <t>Subsea raw-seawater injection pump</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>boosting</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220</v>
+        <v>55000000</v>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>15000000</v>
       </c>
       <c r="G22" t="n">
         <v>0.08</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
         <v>10000</v>
@@ -2424,40 +2440,40 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Includes piggyback cable; topside power supply costed separately</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+          <t>Filters and injects seawater at the seabed — no injection line from the host</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>#C4561B</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0.9</v>
@@ -2466,138 +2482,142 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fl_flex</t>
+          <t>wgc_mod</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flexible flowline</t>
+          <t>Wet-gas compressor module (single train)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>compression</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>200000000</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>60000000</v>
       </c>
       <c r="G23" t="n">
         <v>0.08</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="K23" t="n">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>70</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+        <v>700</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Compact wet-gas compression without upstream separation</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>#3E8A91</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>umb_static</t>
+          <t>sep_gl</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Static steel-tube umbilical</t>
+          <t>Gas–liquid separator with liquid pump</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>umbilical</t>
+          <t>separation</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>900</v>
+        <v>130000000</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>45000000</v>
       </c>
       <c r="G24" t="n">
         <v>0.08</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.25</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K24" t="n">
         <v>10000</v>
@@ -2612,26 +2632,26 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>25</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+        <v>650</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Separates gas from liquid, pumps the liquid; gas flows freely — for long, low-energy tie-backs</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>#E9A23B</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>8 6</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
         <v>0</v>
       </c>
@@ -2642,55 +2662,55 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>umb_dynamic</t>
+          <t>sep_inline</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dynamic umbilical</t>
+          <t>Compact in-line separator / de-watering unit</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>umbilical</t>
+          <t>separation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2500</v>
+        <v>60000000</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="G25" t="n">
         <v>0.08</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
         <v>10000</v>
@@ -2705,26 +2725,26 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>30</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pipe-type separator removing bulk water for reinjection or disposal</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>#C98A1F</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>8 6</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
         <v>0</v>
       </c>
@@ -2735,29 +2755,29 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>slot_tiein</t>
+          <t>sdu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Template slot tie-in (integral)</t>
+          <t>Subsea distribution unit (SDU)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jumper</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2766,24 +2786,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>250000</v>
+        <v>3500000</v>
       </c>
       <c r="F26" t="n">
-        <v>150000</v>
+        <v>1000000</v>
       </c>
       <c r="G26" t="n">
         <v>0.08</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>rig</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
         <v>10000</v>
@@ -2798,30 +2818,26 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>XT landed directly in the template flowbase — no fabricated spool</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>Splits hydraulic, chemical, power and signal lines from the umbilical to several structures</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>#6F6F6F</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>2 3</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
         <v>0</v>
       </c>
@@ -2844,17 +2860,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jumper_rigid</t>
+          <t>uta</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rigid spool/jumper</t>
+          <t>Umbilical termination assembly (UTA)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jumper</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2863,24 +2879,24 @@
         </is>
       </c>
       <c r="E27" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F27" t="n">
         <v>800000</v>
-      </c>
-      <c r="F27" t="n">
-        <v>700000</v>
       </c>
       <c r="G27" t="n">
         <v>0.08</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>ulv</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
         <v>10000</v>
@@ -2899,26 +2915,30 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fabricated after metrology; lead time from metrology</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>Terminates the umbilical at the field; flying leads run on to the trees and structures</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0.9</v>
@@ -2933,43 +2953,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>riser_flex</t>
+          <t>sub_power</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Flexible dynamic riser</t>
+          <t>Subsea power distribution (transformer + VSD)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>riser</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>420</v>
+        <v>55000000</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="G28" t="n">
         <v>0.08</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
         <v>10000</v>
@@ -2978,87 +2998,91 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>120</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+        <v>280</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Step-down transformer and variable-speed drives for pumps or compressors at long step-out</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>#7D4EBF</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>umb_power</t>
+          <t>chem_store</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Electro-hydraulic umbilical with power cores</t>
+          <t>Subsea chemical storage &amp; injection unit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>umbilical</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1500</v>
+        <v>35000000</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="G29" t="n">
         <v>0.08</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K29" t="n">
         <v>10000</v>
@@ -3073,30 +3097,26 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Control, chemical and LV/MV power in one umbilical</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+          <t>Stores and doses chemicals at the seabed; refilled by vessel</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>#B3801A</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>8 6</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
         <v>0</v>
       </c>
@@ -3107,52 +3127,52 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>chem_line</t>
+          <t>riser_base</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chemical injection line (MEG/methanol)</t>
+          <t>Riser base</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>riser_base</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>260</v>
+        <v>3000000</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="G30" t="n">
         <v>0.08</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>14</v>
@@ -3170,30 +3190,22 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Stand-alone bulk chemical line; often piggybacked on the flowline</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>riser_base</t>
+        </is>
+      </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>#9DBA00</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>4 4</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
         <v>0</v>
       </c>
@@ -3216,43 +3228,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gaslift_line</t>
+          <t>host_tiein</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gas lift line</t>
+          <t>Host tie-in modification (topsides)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>host</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>95</v>
+        <v>25000000</v>
       </c>
       <c r="F31" t="n">
-        <v>45</v>
+        <v>15000000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>host</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.35</v>
+        <v>60</v>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K31" t="n">
         <v>10000</v>
@@ -3261,40 +3273,40 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>70</v>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Receiving facilities, pig receiver, control/HPU, chemical injection</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>#5B8FB9</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>10 4</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0.9</v>
@@ -3303,49 +3315,49 @@
         <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>winj_line</t>
+          <t>host_semi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Water injection flowline</t>
+          <t>Host tie-in — semi-submersible</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>host</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>90</v>
+        <v>30000000</v>
       </c>
       <c r="F32" t="n">
-        <v>42</v>
+        <v>18000000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>host</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.35</v>
+        <v>70</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K32" t="n">
         <v>10000</v>
@@ -3354,36 +3366,40 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
+        <v>350</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Floater tie-in: riser porch/pull-in, receiving facilities, utilities</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>semisub</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>110</v>
+      </c>
+      <c r="S32" t="n">
         <v>80</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>#2E86AB</t>
-        </is>
-      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0.9</v>
@@ -3392,49 +3408,49 @@
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>service_line</t>
+          <t>host_fpso</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hydraulic/service line</t>
+          <t>Host tie-in — FPSO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>host</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>180</v>
+        <v>35000000</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>host</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>80</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
         <v>10000</v>
@@ -3449,26 +3465,26 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>8</v>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Turret/swivel slot, riser pull-in, topsides tie-in</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>fpso</t>
+        </is>
+      </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>#8C6D1F</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>3 5</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
         <v>0</v>
       </c>
@@ -3485,46 +3501,46 @@
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fibre_cable</t>
+          <t>fl_rigid_cs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fibre-optic cable</t>
+          <t>Rigid CS flowline (coated)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>flowline</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G34" t="n">
         <v>0.08</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J34" t="n">
         <v>12</v>
@@ -3536,13 +3552,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -3554,22 +3570,18 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>#6F6F6F</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>1 5</t>
-        </is>
-      </c>
+          <t>#00243D</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y34" t="n">
         <v>0.9</v>
@@ -3584,43 +3596,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pwr_cable</t>
+          <t>fl_rigid_cra</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Subsea power cable (HV)</t>
+          <t>Rigid CRA-lined flowline</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>power_cable</t>
+          <t>flowline</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1600</v>
+        <v>260</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G35" t="n">
         <v>0.08</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
         <v>10000</v>
@@ -3629,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -3647,22 +3659,18 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>#C4561B</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2 6</t>
-        </is>
-      </c>
+          <t>#004B6B</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y35" t="n">
         <v>0.9</v>
@@ -3671,6 +3679,1579 @@
         <v>1</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fl_pip</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pipe-in-pipe insulated flowline</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>flowline</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>240</v>
+      </c>
+      <c r="F36" t="n">
+        <v>110</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>plv</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>16</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>14</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>160</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>#0F7A8A</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="W36" t="n">
+        <v>50</v>
+      </c>
+      <c r="X36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fl_deh</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DEH heated rigid flowline</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>flowline</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220</v>
+      </c>
+      <c r="F37" t="n">
+        <v>90</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>plv</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>18</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>14</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>110</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Includes piggyback cable; topside power supply costed separately</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>#C4561B</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>50</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fl_flex</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Flexible flowline</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>flowline</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>210</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>14</v>
+      </c>
+      <c r="K38" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>16</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>70</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>#3E8A91</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fl_tcp</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Thermoplastic composite pipe (TCP) flowline</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>flowline</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>230</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J39" t="n">
+        <v>12</v>
+      </c>
+      <c r="K39" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>10</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>30</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Light, spoolable, corrosion-free; installed from a construction vessel</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>#2E7D6F</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>15</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>jumper_flex</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Flexible jumper</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jumper</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>10</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tolerant of metrology error; no spool fabrication after survey</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>#3E8A91</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>umb_static</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Static steel-tube umbilical</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>umbilical</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>900</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J41" t="n">
+        <v>18</v>
+      </c>
+      <c r="K41" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>25</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>#E9A23B</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8 6</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>umb_dynamic</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Dynamic umbilical</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>umbilical</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>30</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>#C98A1F</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>8 6</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>slot_tiein</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Template slot tie-in (integral)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jumper</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>rig</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>12</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>XT landed directly in the template flowbase — no fabricated spool</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>#6F6F6F</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2 3</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>jumper_rigid</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rigid spool/jumper</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jumper</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>15</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fabricated after metrology; lead time from metrology</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>riser_flex</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Flexible dynamic riser</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>riser</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>420</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>18</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>16</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" t="n">
+        <v>120</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>#7D4EBF</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>30</v>
+      </c>
+      <c r="X45" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>umb_power</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Electro-hydraulic umbilical with power cores</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>umbilical</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>22</v>
+      </c>
+      <c r="K46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>32</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Control, chemical and LV/MV power in one umbilical</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>#B3801A</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>8 6</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>chem_line</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Chemical injection line (MEG/methanol)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>260</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>14</v>
+      </c>
+      <c r="K47" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>12</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stand-alone bulk chemical line; often piggybacked on the flowline</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>#9DBA00</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>4 4</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gaslift_line</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Gas lift line</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>95</v>
+      </c>
+      <c r="F48" t="n">
+        <v>45</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>plv</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J48" t="n">
+        <v>12</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>10</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" t="n">
+        <v>70</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>#5B8FB9</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>10 4</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>winj_line</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Water injection flowline</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>90</v>
+      </c>
+      <c r="F49" t="n">
+        <v>42</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>plv</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J49" t="n">
+        <v>12</v>
+      </c>
+      <c r="K49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>16</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>80</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>#2E86AB</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>service_line</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hydraulic/service line</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>180</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>12</v>
+      </c>
+      <c r="K50" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>8</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>#8C6D1F</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>3 5</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fibre_cable</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Fibre-optic cable</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>120</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>12</v>
+      </c>
+      <c r="K51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>#6F6F6F</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1 5</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>pwr_cable</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Subsea power cable (HV)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>power_cable</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>24</v>
+      </c>
+      <c r="K52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>40</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>#C4561B</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2 6</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA52" t="n">
         <v>1.3</v>
       </c>
     </row>

--- a/library/cost_library_template.xlsx
+++ b/library/cost_library_template.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA52"/>
+  <dimension ref="A1:AA62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -854,17 +854,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tmpl_4slot</t>
+          <t>xt_vxt_5k</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4-slot template + protection</t>
+          <t>Vertical XT 5k</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -873,30 +873,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12000000</v>
+        <v>4500000</v>
       </c>
       <c r="F5" t="n">
-        <v>8000000</v>
+        <v>400000</v>
       </c>
       <c r="G5" t="n">
         <v>0.08</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>rig</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -905,19 +905,23 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>400</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>345 bar (5 000 psi) — low-pressure fields</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>xt</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -943,17 +947,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tmpl_6slot</t>
+          <t>xt_vxt_15k</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6-slot template + protection</t>
+          <t>Vertical XT 15k</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -962,51 +966,55 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16000000</v>
+        <v>9000000</v>
       </c>
       <c r="F6" t="n">
-        <v>11000000</v>
+        <v>800000</v>
       </c>
       <c r="G6" t="n">
         <v>0.08</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>rig</t>
         </is>
       </c>
       <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>55</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1 034 bar (15 000 psi)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>xt</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>600</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>42</v>
-      </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1026,23 +1034,23 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mfld_4slot</t>
+          <t>xt_hxt_20k</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4-slot production manifold</t>
+          <t>Horizontal XT 20k HPHT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>manifold</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1051,30 +1059,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14000000</v>
+        <v>15000000</v>
       </c>
       <c r="F7" t="n">
-        <v>5000000</v>
+        <v>1200000</v>
       </c>
       <c r="G7" t="n">
         <v>0.08</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>rig</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1083,19 +1091,23 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>250</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1 379 bar (20 000 psi) — few qualified suppliers</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>manifold</t>
+          <t>xt</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1115,23 +1127,23 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>plet_std</t>
+          <t>tmpl_4slot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PLET (single hub)</t>
+          <t>4-slot template + protection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>plet</t>
+          <t>template</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1140,30 +1152,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2000000</v>
+        <v>12000000</v>
       </c>
       <c r="F8" t="n">
-        <v>1000000</v>
+        <v>8000000</v>
       </c>
       <c r="G8" t="n">
         <v>0.08</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
         <v>10000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1172,19 +1184,19 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>plet</t>
+          <t>template</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1210,17 +1222,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>plem_std</t>
+          <t>tmpl_6slot</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLEM (multi hub)</t>
+          <t>6-slot template + protection</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>plem</t>
+          <t>template</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1229,30 +1241,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4000000</v>
+        <v>16000000</v>
       </c>
       <c r="F9" t="n">
-        <v>2000000</v>
+        <v>11000000</v>
       </c>
       <c r="G9" t="n">
         <v>0.08</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
         <v>10000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1261,19 +1273,19 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>plet</t>
+          <t>template</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1299,17 +1311,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ilt_std</t>
+          <t>mfld_4slot</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>In-line tee</t>
+          <t>4-slot production manifold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ilt</t>
+          <t>manifold</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1318,30 +1330,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2500000</v>
+        <v>14000000</v>
       </c>
       <c r="F10" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="G10" t="n">
         <v>0.08</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
         <v>10000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1350,19 +1362,19 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ilt</t>
+          <t>manifold</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -1388,17 +1400,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ssiv_std</t>
+          <t>plet_std</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Subsea isolation valve</t>
+          <t>PLET (single hub)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ssiv</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1407,24 +1419,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="F11" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="G11" t="n">
         <v>0.08</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
         <v>10000</v>
@@ -1439,19 +1451,19 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ssiv</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1477,17 +1489,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mpp_2x</t>
+          <t>plem_std</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Multiphase boosting station (2 pumps)</t>
+          <t>PLEM (multi hub)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>boosting</t>
+          <t>plem</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1496,24 +1508,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>90000000</v>
+        <v>4000000</v>
       </c>
       <c r="F12" t="n">
-        <v>25000000</v>
+        <v>2000000</v>
       </c>
       <c r="G12" t="n">
         <v>0.08</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>10000</v>
@@ -1528,19 +1540,19 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1560,23 +1572,23 @@
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>comp_station</t>
+          <t>ilt_std</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Subsea compression station</t>
+          <t>In-line tee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>compression</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1585,24 +1597,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>450000000</v>
+        <v>2500000</v>
       </c>
       <c r="F13" t="n">
-        <v>150000000</v>
+        <v>1000000</v>
       </c>
       <c r="G13" t="n">
         <v>0.08</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
         <v>10000</v>
@@ -1617,19 +1629,19 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -1643,29 +1655,29 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sep_station</t>
+          <t>ssiv_std</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Subsea separation + water reinjection</t>
+          <t>Subsea isolation valve</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>ssiv</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1674,24 +1686,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>180000000</v>
+        <v>6000000</v>
       </c>
       <c r="F14" t="n">
-        <v>70000000</v>
+        <v>1500000</v>
       </c>
       <c r="G14" t="n">
         <v>0.08</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
         <v>10000</v>
@@ -1706,19 +1718,19 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ssiv</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -1732,29 +1744,29 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>plet_valved</t>
+          <t>mpp_2x</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PLET with isolation valve</t>
+          <t>Multiphase boosting station (2 pumps)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>plet</t>
+          <t>boosting</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1763,24 +1775,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3200000</v>
+        <v>90000000</v>
       </c>
       <c r="F15" t="n">
-        <v>1400000</v>
+        <v>25000000</v>
       </c>
       <c r="G15" t="n">
         <v>0.08</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
         <v>10000</v>
@@ -1795,23 +1807,19 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>45</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Remote-operated valve lets the line be isolated at the end structure</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>plet</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1831,23 +1839,23 @@
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>plet_pig</t>
+          <t>comp_station</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PLET with subsea pig launcher/receiver</t>
+          <t>Subsea compression station</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>plet</t>
+          <t>compression</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1856,24 +1864,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4500000</v>
+        <v>450000000</v>
       </c>
       <c r="F16" t="n">
-        <v>2000000</v>
+        <v>150000000</v>
       </c>
       <c r="G16" t="n">
         <v>0.08</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="K16" t="n">
         <v>10000</v>
@@ -1888,23 +1896,19 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>70</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>For single-line (non-looped) systems that still need pigging</t>
-        </is>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>plet</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -1918,29 +1922,29 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wye_pig</t>
+          <t>sep_station</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Piggable wye (Y-piece)</t>
+          <t>Subsea separation + water reinjection</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ilt</t>
+          <t>separation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1949,24 +1953,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3000000</v>
+        <v>180000000</v>
       </c>
       <c r="F17" t="n">
-        <v>1200000</v>
+        <v>70000000</v>
       </c>
       <c r="G17" t="n">
         <v>0.08</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="K17" t="n">
         <v>10000</v>
@@ -1981,23 +1985,19 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Joins two lines into one while keeping it piggable</t>
-        </is>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ilt</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2011,29 +2011,29 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hot_tap</t>
+          <t>plet_valved</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hot-tap tie-in to an operating pipeline</t>
+          <t>PLET with isolation valve</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ilt</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2042,24 +2042,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6000000</v>
+        <v>3200000</v>
       </c>
       <c r="F18" t="n">
-        <v>2000000</v>
+        <v>1400000</v>
       </c>
       <c r="G18" t="n">
         <v>0.08</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>10000</v>
@@ -2074,23 +2074,23 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tee welded/clamped onto a live line; includes hot-tap machine and diving/ROV spread time</t>
+          <t>Remote-operated valve lets the line be isolated at the end structure</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ilt</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -2110,23 +2110,23 @@
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hipps_mod</t>
+          <t>plet_pig</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HIPPS module (subsea)</t>
+          <t>PLET with subsea pig launcher/receiver</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ssiv</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12000000</v>
+        <v>4500000</v>
       </c>
       <c r="F19" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="G19" t="n">
         <v>0.08</v>
@@ -2152,7 +2152,7 @@
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
         <v>10000</v>
@@ -2167,20 +2167,20 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tick HIPPS on the node so lines downstream may be de-rated</t>
+          <t>For single-line (non-looped) systems that still need pigging</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ssiv</t>
+          <t>plet</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2209,17 +2209,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pump_1ph</t>
+          <t>wye_pig</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Single-phase booster pump station (liquid)</t>
+          <t>Piggable wye (Y-piece)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>boosting</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2228,24 +2228,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>45000000</v>
+        <v>3000000</v>
       </c>
       <c r="F20" t="n">
-        <v>15000000</v>
+        <v>1200000</v>
       </c>
       <c r="G20" t="n">
         <v>0.08</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
         <v>10000</v>
@@ -2260,23 +2260,23 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Centrifugal pump for oil or water with low gas fraction (typically GVF &lt; 15 %)</t>
+          <t>Joins two lines into one while keeping it piggable</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -2296,23 +2296,23 @@
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pump_mp1</t>
+          <t>hot_tap</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Multiphase pump module (single, retrievable)</t>
+          <t>Hot-tap tie-in to an operating pipeline</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>boosting</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2321,24 +2321,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>50000000</v>
+        <v>6000000</v>
       </c>
       <c r="F21" t="n">
-        <v>15000000</v>
+        <v>2000000</v>
       </c>
       <c r="G21" t="n">
         <v>0.08</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
         <v>10000</v>
@@ -2353,23 +2353,23 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Helico-axial or twin-screw; handles high gas fractions without separation</t>
+          <t>Tee welded/clamped onto a live line; includes hot-tap machine and diving/ROV spread time</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ilt</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -2395,17 +2395,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>winj_pump</t>
+          <t>hipps_mod</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Subsea raw-seawater injection pump</t>
+          <t>HIPPS module (subsea)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>boosting</t>
+          <t>ssiv</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2414,24 +2414,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>55000000</v>
+        <v>12000000</v>
       </c>
       <c r="F22" t="n">
-        <v>15000000</v>
+        <v>3000000</v>
       </c>
       <c r="G22" t="n">
         <v>0.08</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
         <v>10000</v>
@@ -2446,23 +2446,23 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Filters and injects seawater at the seabed — no injection line from the host</t>
+          <t>Tick HIPPS on the node so lines downstream may be de-rated</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ssiv</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -2482,23 +2482,23 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wgc_mod</t>
+          <t>pump_1ph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wet-gas compressor module (single train)</t>
+          <t>Single-phase booster pump station (liquid)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>compression</t>
+          <t>boosting</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>200000000</v>
+        <v>45000000</v>
       </c>
       <c r="F23" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="G23" t="n">
         <v>0.08</v>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
         <v>10000</v>
@@ -2539,11 +2539,11 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Compact wet-gas compression without upstream separation</t>
+          <t>Centrifugal pump for oil or water with low gas fraction (typically GVF &lt; 15 %)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -2569,29 +2569,29 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sep_gl</t>
+          <t>pump_mp1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gas–liquid separator with liquid pump</t>
+          <t>Multiphase pump module (single, retrievable)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>boosting</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>130000000</v>
+        <v>50000000</v>
       </c>
       <c r="F24" t="n">
-        <v>45000000</v>
+        <v>15000000</v>
       </c>
       <c r="G24" t="n">
         <v>0.08</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
         <v>10000</v>
@@ -2632,11 +2632,11 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>650</v>
+        <v>180</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Separates gas from liquid, pumps the liquid; gas flows freely — for long, low-energy tie-backs</t>
+          <t>Helico-axial or twin-screw; handles high gas fractions without separation</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
@@ -2662,29 +2662,29 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sep_inline</t>
+          <t>winj_pump</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Compact in-line separator / de-watering unit</t>
+          <t>Subsea raw-seawater injection pump</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>boosting</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>60000000</v>
+        <v>55000000</v>
       </c>
       <c r="F25" t="n">
-        <v>20000000</v>
+        <v>15000000</v>
       </c>
       <c r="G25" t="n">
         <v>0.08</v>
@@ -2725,11 +2725,11 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pipe-type separator removing bulk water for reinjection or disposal</t>
+          <t>Filters and injects seawater at the seabed — no injection line from the host</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
@@ -2755,29 +2755,29 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sdu</t>
+          <t>wgc_mod</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Subsea distribution unit (SDU)</t>
+          <t>Wet-gas compressor module (single train)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>compression</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2786,24 +2786,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3500000</v>
+        <v>200000000</v>
       </c>
       <c r="F26" t="n">
-        <v>1000000</v>
+        <v>60000000</v>
       </c>
       <c r="G26" t="n">
         <v>0.08</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K26" t="n">
         <v>10000</v>
@@ -2818,23 +2818,23 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>30</v>
+        <v>700</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Splits hydraulic, chemical, power and signal lines from the umbilical to several structures</t>
+          <t>Compact wet-gas compression without upstream separation</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -2848,29 +2848,29 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>uta</t>
+          <t>sep_gl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Umbilical termination assembly (UTA)</t>
+          <t>Gas–liquid separator with liquid pump</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>separation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2879,24 +2879,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2000000</v>
+        <v>130000000</v>
       </c>
       <c r="F27" t="n">
-        <v>800000</v>
+        <v>45000000</v>
       </c>
       <c r="G27" t="n">
         <v>0.08</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n">
         <v>10000</v>
@@ -2911,23 +2911,23 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>650</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Terminates the umbilical at the field; flying leads run on to the trees and structures</t>
+          <t>Separates gas from liquid, pumps the liquid; gas flows freely — for long, low-energy tie-backs</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -2941,29 +2941,29 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z27" t="n">
         <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sub_power</t>
+          <t>sep_inline</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Subsea power distribution (transformer + VSD)</t>
+          <t>Compact in-line separator / de-watering unit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>separation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>55000000</v>
+        <v>60000000</v>
       </c>
       <c r="F28" t="n">
-        <v>15000000</v>
+        <v>20000000</v>
       </c>
       <c r="G28" t="n">
         <v>0.08</v>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K28" t="n">
         <v>10000</v>
@@ -3004,23 +3004,23 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Step-down transformer and variable-speed drives for pumps or compressors at long step-out</t>
+          <t>Pipe-type separator removing bulk water for reinjection or disposal</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
@@ -3040,18 +3040,18 @@
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chem_store</t>
+          <t>sdu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Subsea chemical storage &amp; injection unit</t>
+          <t>Subsea distribution unit (SDU)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3065,24 +3065,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>35000000</v>
+        <v>3500000</v>
       </c>
       <c r="F29" t="n">
-        <v>10000000</v>
+        <v>1000000</v>
       </c>
       <c r="G29" t="n">
         <v>0.08</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>hlv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
         <v>10000</v>
@@ -3097,11 +3097,11 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stores and doses chemicals at the seabed; refilled by vessel</t>
+          <t>Splits hydraulic, chemical, power and signal lines from the umbilical to several structures</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -3127,29 +3127,29 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>riser_base</t>
+          <t>uta</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Riser base</t>
+          <t>Umbilical termination assembly (UTA)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>riser_base</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3158,24 +3158,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="F30" t="n">
-        <v>2000000</v>
+        <v>800000</v>
       </c>
       <c r="G30" t="n">
         <v>0.08</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>ulv</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K30" t="n">
         <v>10000</v>
@@ -3190,19 +3190,23 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>120</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Terminates the umbilical at the field; flying leads run on to the trees and structures</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>riser_base</t>
+          <t>control</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3228,17 +3232,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>host_tiein</t>
+          <t>sub_power</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Host tie-in modification (topsides)</t>
+          <t>Subsea power distribution (transformer + VSD)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3247,24 +3251,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>25000000</v>
+        <v>55000000</v>
       </c>
       <c r="F31" t="n">
         <v>15000000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n">
         <v>10000</v>
@@ -3279,23 +3283,23 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Receiving facilities, pig receiver, control/HPU, chemical injection</t>
+          <t>Step-down transformer and variable-speed drives for pumps or compressors at long step-out</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>control</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="S31" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -3309,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -3321,17 +3325,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>host_semi</t>
+          <t>chem_store</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Host tie-in — semi-submersible</t>
+          <t>Subsea chemical storage &amp; injection unit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3340,24 +3344,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>30000000</v>
+        <v>35000000</v>
       </c>
       <c r="F32" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>hlv</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K32" t="n">
         <v>10000</v>
@@ -3372,23 +3376,23 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Floater tie-in: riser porch/pull-in, receiving facilities, utilities</t>
+          <t>Stores and doses chemicals at the seabed; refilled by vessel</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>semisub</t>
+          <t>control</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="S32" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3402,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
@@ -3414,17 +3418,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>host_fpso</t>
+          <t>riser_base</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Host tie-in — FPSO</t>
+          <t>Riser base</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>riser_base</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3433,24 +3437,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>35000000</v>
+        <v>3000000</v>
       </c>
       <c r="F33" t="n">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
         <v>10000</v>
@@ -3465,23 +3469,19 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>400</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Turret/swivel slot, riser pull-in, topsides tie-in</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>fpso</t>
+          <t>riser_base</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>280</v>
+        <v>14</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -3501,49 +3501,49 @@
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fl_rigid_cs</t>
+          <t>host_tiein</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rigid CS flowline (coated)</t>
+          <t>Host tie-in modification (topsides)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>host</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>95</v>
+        <v>25000000</v>
       </c>
       <c r="F34" t="n">
-        <v>45</v>
+        <v>15000000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>host</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.35</v>
+        <v>60</v>
       </c>
       <c r="J34" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K34" t="n">
         <v>10000</v>
@@ -3552,36 +3552,40 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>90</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Receiving facilities, pig receiver, control/HPU, chemical injection</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>#00243D</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0.9</v>
@@ -3590,49 +3594,49 @@
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fl_rigid_cra</t>
+          <t>host_semi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rigid CRA-lined flowline</t>
+          <t>Host tie-in — semi-submersible</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>host</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>260</v>
+        <v>30000000</v>
       </c>
       <c r="F35" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>70</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>plv</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.4</v>
-      </c>
       <c r="J35" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K35" t="n">
         <v>10000</v>
@@ -3641,36 +3645,40 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>95</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Floater tie-in: riser porch/pull-in, receiving facilities, utilities</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>semisub</t>
+        </is>
+      </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>#004B6B</t>
-        </is>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0.9</v>
@@ -3679,49 +3687,49 @@
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fl_pip</t>
+          <t>host_fpso</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pipe-in-pipe insulated flowline</t>
+          <t>Host tie-in — FPSO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>flowline</t>
+          <t>host</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>240</v>
+        <v>35000000</v>
       </c>
       <c r="F36" t="n">
-        <v>110</v>
+        <v>20000000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>host</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>80</v>
       </c>
       <c r="J36" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
         <v>10000</v>
@@ -3730,36 +3738,40 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>160</v>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Turret/swivel slot, riser pull-in, topsides tie-in</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>fpso</t>
+        </is>
+      </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>#0F7A8A</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0.9</v>
@@ -3768,18 +3780,18 @@
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fl_deh</t>
+          <t>fl_rigid_cs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DEH heated rigid flowline</t>
+          <t>Rigid CS flowline (coated)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3793,10 +3805,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="F37" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="G37" t="n">
         <v>0.08</v>
@@ -3807,10 +3819,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="J37" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
         <v>10000</v>
@@ -3819,19 +3831,15 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
-        <v>110</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Includes piggyback cable; topside power supply costed separately</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
         <v>0</v>
@@ -3841,7 +3849,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>#C4561B</t>
+          <t>#00243D</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
@@ -3849,10 +3857,10 @@
         <v>0.75</v>
       </c>
       <c r="W37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="Y37" t="n">
         <v>0.9</v>
@@ -3867,12 +3875,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fl_flex</t>
+          <t>fl_rigid_cra</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Flexible flowline</t>
+          <t>Rigid CRA-lined flowline</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3886,27 +3894,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G38" t="n">
         <v>0.08</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3915,10 +3923,10 @@
         <v>16</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -3930,18 +3938,18 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>#3E8A91</t>
+          <t>#004B6B</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="Y38" t="n">
         <v>0.9</v>
@@ -3956,12 +3964,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fl_tcp</t>
+          <t>fl_pip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thermoplastic composite pipe (TCP) flowline</t>
+          <t>Pipe-in-pipe insulated flowline</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3975,24 +3983,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G39" t="n">
         <v>0.08</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
         <v>10000</v>
@@ -4001,19 +4009,15 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
-        <v>30</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Light, spoolable, corrosion-free; installed from a construction vessel</t>
-        </is>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
         <v>0</v>
@@ -4023,18 +4027,18 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>#2E7D6F</t>
+          <t>#0F7A8A</t>
         </is>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W39" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y39" t="n">
         <v>0.9</v>
@@ -4049,43 +4053,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jumper_flex</t>
+          <t>fl_deh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Flexible jumper</t>
+          <t>DEH heated rigid flowline</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jumper</t>
+          <t>flowline</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>600000</v>
+        <v>220</v>
       </c>
       <c r="F40" t="n">
-        <v>100000</v>
+        <v>90</v>
       </c>
       <c r="G40" t="n">
         <v>0.08</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
         <v>10000</v>
@@ -4094,17 +4098,17 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tolerant of metrology error; no spool fabrication after survey</t>
+          <t>Includes piggyback cable; topside power supply costed separately</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
@@ -4116,18 +4120,18 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>#3E8A91</t>
+          <t>#C4561B</t>
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y40" t="n">
         <v>0.9</v>
@@ -4142,26 +4146,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>umb_static</t>
+          <t>fl_flex</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Static steel-tube umbilical</t>
+          <t>Flexible flowline</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>umbilical</t>
+          <t>flowline</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>900</v>
+        <v>210</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -4171,29 +4175,29 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -4205,22 +4209,18 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>#E9A23B</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>8 6</t>
-        </is>
-      </c>
+          <t>#3E8A91</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y41" t="n">
         <v>0.9</v>
@@ -4235,26 +4235,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>umb_dynamic</t>
+          <t>fl_tcp</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dynamic umbilical</t>
+          <t>Thermoplastic composite pipe (TCP) flowline</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>umbilical</t>
+          <t>flowline</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2500</v>
+        <v>230</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -4264,14 +4264,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J42" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
         <v>10000</v>
@@ -4280,15 +4280,19 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
         <v>30</v>
       </c>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Light, spoolable, corrosion-free; installed from a construction vessel</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
         <v>0</v>
@@ -4298,19 +4302,15 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>#C98A1F</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>8 6</t>
-        </is>
-      </c>
+          <t>#2E7D6F</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -4328,12 +4328,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>slot_tiein</t>
+          <t>jumper_flex</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Template slot tie-in (integral)</t>
+          <t>Flexible jumper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4347,24 +4347,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>250000</v>
+        <v>600000</v>
       </c>
       <c r="F43" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="G43" t="n">
         <v>0.08</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>rig</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
         <v>10000</v>
@@ -4379,11 +4379,11 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>XT landed directly in the template flowbase — no fabricated spool</t>
+          <t>Tolerant of metrology error; no spool fabrication after survey</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
@@ -4395,14 +4395,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>#6F6F6F</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>2 3</t>
-        </is>
-      </c>
+          <t>#3E8A91</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
         <v>0</v>
       </c>
@@ -4425,43 +4421,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>jumper_rigid</t>
+          <t>umb_static</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rigid spool/jumper</t>
+          <t>Static steel-tube umbilical</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jumper</t>
+          <t>umbilical</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>per_m</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>800000</v>
+        <v>900</v>
       </c>
       <c r="F44" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0.08</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>ulv</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
         <v>10000</v>
@@ -4476,13 +4472,9 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>15</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Fabricated after metrology; lead time from metrology</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
         <v>0</v>
@@ -4490,16 +4482,24 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>#E9A23B</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>8 6</t>
+        </is>
+      </c>
       <c r="V44" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0.9</v>
@@ -4514,26 +4514,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>riser_flex</t>
+          <t>umb_dynamic</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Flexible dynamic riser</t>
+          <t>Dynamic umbilical</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>riser</t>
+          <t>umbilical</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>per_inch_m</t>
+          <t>per_m</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>420</v>
+        <v>2500</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4543,14 +4543,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>ulv</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
         <v>10000</v>
@@ -4559,13 +4559,13 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
@@ -4577,18 +4577,22 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>#7D4EBF</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
+          <t>#C98A1F</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8 6</t>
+        </is>
+      </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0.9</v>
@@ -4603,43 +4607,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>umb_power</t>
+          <t>slot_tiein</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Electro-hydraulic umbilical with power cores</t>
+          <t>Template slot tie-in (integral)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>umbilical</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1500</v>
+        <v>250000</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G46" t="n">
         <v>0.08</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>rig</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K46" t="n">
         <v>10000</v>
@@ -4654,11 +4658,11 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Control, chemical and LV/MV power in one umbilical</t>
+          <t>XT landed directly in the template flowbase — no fabricated spool</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr"/>
@@ -4670,12 +4674,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>#B3801A</t>
+          <t>#6F6F6F</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>8 6</t>
+          <t>2 3</t>
         </is>
       </c>
       <c r="V46" t="n">
@@ -4700,43 +4704,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>chem_line</t>
+          <t>jumper_rigid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chemical injection line (MEG/methanol)</t>
+          <t>Rigid spool/jumper</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>260</v>
+        <v>800000</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="G47" t="n">
         <v>0.08</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
         <v>10000</v>
@@ -4751,11 +4755,11 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stand-alone bulk chemical line; often piggybacked on the flowline</t>
+          <t>Fabricated after metrology; lead time from metrology</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr"/>
@@ -4765,24 +4769,16 @@
       <c r="S47" t="n">
         <v>0</v>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>#9DBA00</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>4 4</t>
-        </is>
-      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y47" t="n">
         <v>0.9</v>
@@ -4797,17 +4793,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gaslift_line</t>
+          <t>riser_flex</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gas lift line</t>
+          <t>Flexible dynamic riser</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>riser</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4816,24 +4812,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>95</v>
+        <v>420</v>
       </c>
       <c r="F48" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0.08</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
         <v>10000</v>
@@ -4842,13 +4838,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -4860,22 +4856,18 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>#5B8FB9</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>10 4</t>
-        </is>
-      </c>
+          <t>#7D4EBF</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="X48" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="Y48" t="n">
         <v>0.9</v>
@@ -4890,17 +4882,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>winj_line</t>
+          <t>riser_flex_lw</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Water injection flowline</t>
+          <t>Flexible lazy-wave riser (with buoyancy)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>riser</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4909,24 +4901,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0.08</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>plv</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.35</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
         <v>10000</v>
@@ -4941,9 +4933,13 @@
         <v>4</v>
       </c>
       <c r="O49" t="n">
-        <v>80</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Buoyancy section decouples floater motion — deeper water or larger offsets</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
         <v>0</v>
@@ -4953,18 +4949,18 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>#2E86AB</t>
+          <t>#9467BD</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="X49" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="Y49" t="n">
         <v>0.9</v>
@@ -4979,43 +4975,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>service_line</t>
+          <t>riser_scr</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hydraulic/service line</t>
+          <t>Steel catenary riser (SCR)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>riser</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G50" t="n">
         <v>0.08</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K50" t="n">
         <v>10000</v>
@@ -5024,15 +5020,19 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Low-motion hosts (TLP, spar, semi in deep water); fatigue at the touchdown point governs</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="n">
         <v>0</v>
@@ -5042,22 +5042,18 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>#8C6D1F</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>3 5</t>
-        </is>
-      </c>
+          <t>#5E3A9E</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y50" t="n">
         <v>0.9</v>
@@ -5072,43 +5068,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fibre_cable</t>
+          <t>riser_slwr</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fibre-optic cable</t>
+          <t>Steel lazy-wave riser (SLWR)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>utility_line</t>
+          <t>riser</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G51" t="n">
         <v>0.08</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>plv</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
         <v>10000</v>
@@ -5117,15 +5113,19 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O51" t="n">
-        <v>5</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Steel riser with buoyancy for turret-moored FPSOs and harsh-environment motions</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
         <v>0</v>
@@ -5135,22 +5135,18 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>#6F6F6F</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1 5</t>
-        </is>
-      </c>
+          <t>#4B2E83</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y51" t="n">
         <v>0.9</v>
@@ -5165,43 +5161,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>pwr_cable</t>
+          <t>riser_ttr</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Subsea power cable (HV)</t>
+          <t>Top-tensioned riser (TTR)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>power_cable</t>
+          <t>riser</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>per_m</t>
+          <t>per_inch_m</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1600</v>
+        <v>320</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G52" t="n">
         <v>0.08</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ulv</t>
+          <t>rig</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K52" t="n">
         <v>10000</v>
@@ -5210,15 +5206,19 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
-        <v>40</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
+        <v>180</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vertical riser tensioned from a TLP or spar; allows dry trees</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="n">
         <v>0</v>
@@ -5228,22 +5228,18 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>#C4561B</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>2 6</t>
-        </is>
-      </c>
+          <t>#7B3FA0</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y52" t="n">
         <v>0.9</v>
@@ -5252,6 +5248,940 @@
         <v>1</v>
       </c>
       <c r="AA52" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>riser_hybrid</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Hybrid riser tower / free-standing riser</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>riser</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>600</v>
+      </c>
+      <c r="F53" t="n">
+        <v>250</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>hlv</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>30</v>
+      </c>
+      <c r="K53" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>20</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6</v>
+      </c>
+      <c r="O53" t="n">
+        <v>250</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Buoyancy-can tensioned steel riser with flexible jumpers to the host; very deep water</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>#3C1F66</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>40</v>
+      </c>
+      <c r="X53" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>riser_rigid_fixed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rigid riser clamped to a fixed platform</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>riser</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>160</v>
+      </c>
+      <c r="F54" t="n">
+        <v>120</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>hlv</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>14</v>
+      </c>
+      <c r="K54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>30</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>140</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Pre-installed or retrofitted riser on a jacket, with a spool to the pipeline</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>#6A4C93</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>riser_jtube</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>J-tube pull-in riser</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>riser</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>140</v>
+      </c>
+      <c r="F55" t="n">
+        <v>60</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" t="n">
+        <v>12</v>
+      </c>
+      <c r="K55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>16</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>100</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Line or umbilical pulled up through a J-tube on a fixed platform — uses a spare J-tube</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>#8A6BBE</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>umb_power</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Electro-hydraulic umbilical with power cores</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>umbilical</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>22</v>
+      </c>
+      <c r="K56" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>32</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Control, chemical and LV/MV power in one umbilical</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>#B3801A</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>8 6</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>chem_line</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chemical injection line (MEG/methanol)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>14</v>
+      </c>
+      <c r="K57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>12</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stand-alone bulk chemical line; often piggybacked on the flowline</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>#9DBA00</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>4 4</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>gaslift_line</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gas lift line</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>95</v>
+      </c>
+      <c r="F58" t="n">
+        <v>45</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>plv</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J58" t="n">
+        <v>12</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>70</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>#5B8FB9</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>10 4</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>winj_line</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Water injection flowline</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>per_inch_m</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>90</v>
+      </c>
+      <c r="F59" t="n">
+        <v>42</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>plv</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J59" t="n">
+        <v>12</v>
+      </c>
+      <c r="K59" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>16</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>80</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>#2E86AB</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>service_line</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hydraulic/service line</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>180</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>12</v>
+      </c>
+      <c r="K60" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>8</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>#8C6D1F</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>3 5</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fibre_cable</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fibre-optic cable</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>utility_line</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>120</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J61" t="n">
+        <v>12</v>
+      </c>
+      <c r="K61" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>5</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>#6F6F6F</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1 5</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>pwr_cable</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Subsea power cable (HV)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>power_cable</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>per_m</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ulv</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>24</v>
+      </c>
+      <c r="K62" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>40</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>#C4561B</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2 6</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" t="n">
         <v>1.3</v>
       </c>
     </row>
